--- a/inst/sap-pipeline/03_ars/ARS_STUDY01.xlsx
+++ b/inst/sap-pipeline/03_ars/ARS_STUDY01.xlsx
@@ -387,7 +387,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ydisctools 0.0.240 build_ars()</t>
+          <t>ydisctools 0.0.244 build_ars()</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary</t>
+          <t>Mth_categorical_summary_flat</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_num</t>
+          <t>Mth_categorical_summary_flat_pct_num</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_den</t>
+          <t>Mth_categorical_summary_flat_pct_den</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary</t>
+          <t>Mth_categorical_summary_flat</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_num</t>
+          <t>Mth_categorical_summary_flat_pct_num</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_den</t>
+          <t>Mth_categorical_summary_flat_pct_den</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary</t>
+          <t>Mth_categorical_summary_flat</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_num</t>
+          <t>Mth_categorical_summary_flat_pct_num</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_den</t>
+          <t>Mth_categorical_summary_flat_pct_den</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary</t>
+          <t>Mth_categorical_summary_flat</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_num</t>
+          <t>Mth_categorical_summary_flat_pct_num</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_den</t>
+          <t>Mth_categorical_summary_flat_pct_den</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary</t>
+          <t>Mth_categorical_summary_flat</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_num</t>
+          <t>Mth_categorical_summary_flat_pct_num</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_den</t>
+          <t>Mth_categorical_summary_flat_pct_den</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary</t>
+          <t>Mth_categorical_summary_flat</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_num</t>
+          <t>Mth_categorical_summary_flat_pct_num</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_den</t>
+          <t>Mth_categorical_summary_flat_pct_den</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary</t>
+          <t>Mth_categorical_summary_flat</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_num</t>
+          <t>Mth_categorical_summary_flat_pct_num</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_den</t>
+          <t>Mth_categorical_summary_flat_pct_den</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3269,7 +3269,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). A flat analysis (no category variable, e.g. 'subjects with at least one TEAE') tabulates a constant flag with the group as `by=`, so the percentage denominator is the per-group big N rather than the overall N. ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
+          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). Flat analyses (no category variable) are generated from the dedicated categorical_summary_flat template instead. ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). A flat analysis (no category variable, e.g. 'subjects with at least one TEAE') tabulates a constant flag with the group as `by=`, so the percentage denominator is the per-group big N rather than the overall N. ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
+          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). Flat analyses (no category variable) are generated from the dedicated categorical_summary_flat template instead. ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3809,6 +3809,96 @@
         </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>(xx.x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Subject count per group (n and %)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Flat n (%)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Distinct-subject n and percentage per group for a flat analysis (no category variable, e.g. 'subjects with at least one TEAE'), with a referenced denominator analysis. Tabulates a constant '.flag_' with the group as `by=`, so the percentage denominator is that group's big N. Selected automatically by build_ars() when a categorical_summary analysis has a single grouping and variable = USUBJID; the compact parameter format keeps the categorical_summary key. ydisctools overlay entry.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat_op1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>xx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Subject count per group (n and %)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Flat n (%)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Distinct-subject n and percentage per group for a flat analysis (no category variable, e.g. 'subjects with at least one TEAE'), with a referenced denominator analysis. Tabulates a constant '.flag_' with the group as `by=`, so the percentage denominator is that group's big N. Selected automatically by build_ars() when a categorical_summary analysis has a single grouping and variable = USUBJID; the compact parameter format keeps the categorical_summary key. ydisctools overlay entry.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat_op2</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>(xx.x)</t>
         </is>
@@ -3821,7 +3911,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3934,16 +4024,9 @@
   dplyr::select(denom_anagroupvarshere)
 in_data = df2_analysisidhere |&gt;
     dplyr::distinct(distinctlisthere)
+# strata= when the innermost grouping is data-driven, by= when pre-defined
 dataDriven = isdatadrivenhere
-if(ncol(in_data) &lt;= 2){
-# flat analysis (no category variable): tabulate a constant flag with the
-# group as `by`, so the percentage denominator is the per-group big N
-df3_analysisidhere &lt;-
-  cards::ard_tabulate(
-    data = in_data |&gt; dplyr::mutate(.flag_ = 'Y')
-    , by = 'denom_anagroupvarshere', variables = '.flag_',
-    denominator = denom_dataset
-  ) } else if(dataDriven == TRUE){
+if(dataDriven == TRUE){
 df3_analysisidhere &lt;-
   cards::ard_tabulate(
     data = in_data
@@ -3963,6 +4046,44 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R (siera)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>denom_dataset = df2_denomanaidhere |&gt;
+  dplyr::select(denom_anagroupvarshere)
+# n (%) of subjects per group: tabulate a constant flag with the group as
+# `by`, so the percentage denominator is that group's big N
+in_data = df2_analysisidhere |&gt;
+    dplyr::distinct(distinctlisthere) |&gt;
+    dplyr::mutate(.flag_ = 'Y')
+df3_analysisidhere &lt;-
+  cards::ard_tabulate(
+    data = in_data
+    , by = 'denom_anagroupvarshere', variables = '.flag_',
+    denominator = denom_dataset
+  )
+df3_analysisidhere &lt;- df3_analysisidhere |&gt;
+  dplyr::filter(stat_name %in% c('n', 'p')) |&gt;
+  dplyr::mutate(operationid = dplyr::case_when(stat_name == 'n' ~ 'opid1here',
+                                               stat_name == 'p' ~ 'opid2here'))</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3970,7 +4091,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4299,6 +4420,87 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>strata_vars</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>distinctlisthere</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Grouping variable + analysis variable, comma separated</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>distinct list</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>distinct_list</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>denomanaidhere</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Analysis ID supplying the denominator</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>denom ana id</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DEN_analysisid</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>denom_anagroupvarshere</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Grouping variable of the denominator analysis</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>denom grp var</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AG_denom_var1</t>
         </is>
       </c>
     </row>
